--- a/exports/RVNL_full_report.xlsx
+++ b/exports/RVNL_full_report.xlsx
@@ -18,9 +18,11 @@
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <numFmts count="2">
+  <numFmts count="4">
     <numFmt numFmtId="164" formatCode="yyyy-mm-dd h:mm:ss"/>
     <numFmt numFmtId="165" formatCode="YYYY-MM-DD HH:MM:SS"/>
+    <numFmt numFmtId="166" formatCode="yyyy-mm-dd"/>
+    <numFmt numFmtId="167" formatCode="YYYY-MM-DD"/>
   </numFmts>
   <fonts count="1">
     <font>
@@ -51,10 +53,11 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="3">
+  <cellXfs count="4">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="165" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="1" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="167" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0" hidden="0"/>
@@ -420,7 +423,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:Q67"/>
+  <dimension ref="A1:U67"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -509,6 +512,26 @@
           <t>candles_held</t>
         </is>
       </c>
+      <c r="R1" t="inlineStr">
+        <is>
+          <t>expiry</t>
+        </is>
+      </c>
+      <c r="S1" t="inlineStr">
+        <is>
+          <t>reached_expiry</t>
+        </is>
+      </c>
+      <c r="T1" t="inlineStr">
+        <is>
+          <t>rule_trades</t>
+        </is>
+      </c>
+      <c r="U1" t="inlineStr">
+        <is>
+          <t>rule_wins</t>
+        </is>
+      </c>
     </row>
     <row r="2">
       <c r="A2" t="inlineStr">
@@ -534,19 +557,19 @@
         <v>4.82</v>
       </c>
       <c r="G2" s="1" t="n">
-        <v>44582.55208333334</v>
+        <v>44585.38541666666</v>
       </c>
       <c r="H2" t="n">
-        <v>37.2</v>
+        <v>35.6</v>
       </c>
       <c r="I2" t="n">
         <v>36.04736457366064</v>
       </c>
       <c r="J2" s="2" t="n">
-        <v>11.16666666666667</v>
+        <v>14</v>
       </c>
       <c r="K2" t="n">
-        <v>3.33</v>
+        <v>-1.11</v>
       </c>
       <c r="L2" t="n">
         <v>1.94</v>
@@ -555,7 +578,7 @@
         <v>0.93</v>
       </c>
       <c r="N2" t="n">
-        <v>2.21</v>
+        <v>4.3</v>
       </c>
       <c r="O2" t="n">
         <v>0.5600000000000001</v>
@@ -564,7 +587,19 @@
         <v>0</v>
       </c>
       <c r="Q2" t="n">
-        <v>20</v>
+        <v>21</v>
+      </c>
+      <c r="R2" s="3" t="n">
+        <v>44588</v>
+      </c>
+      <c r="S2" t="b">
+        <v>0</v>
+      </c>
+      <c r="T2" t="n">
+        <v>1</v>
+      </c>
+      <c r="U2" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="3">
@@ -591,19 +626,19 @@
         <v>11.69</v>
       </c>
       <c r="G3" s="1" t="n">
-        <v>44629.38541666666</v>
+        <v>44629.55208333334</v>
       </c>
       <c r="H3" t="n">
-        <v>31.65</v>
+        <v>32.25</v>
       </c>
       <c r="I3" t="n">
         <v>32.08035750857241</v>
       </c>
       <c r="J3" s="2" t="n">
-        <v>44</v>
+        <v>44.16666666666666</v>
       </c>
       <c r="K3" t="n">
-        <v>11.1</v>
+        <v>9.41</v>
       </c>
       <c r="L3" t="n">
         <v>5.06</v>
@@ -621,7 +656,19 @@
         <v>1</v>
       </c>
       <c r="Q3" t="n">
-        <v>61</v>
+        <v>62</v>
+      </c>
+      <c r="R3" s="3" t="n">
+        <v>44588</v>
+      </c>
+      <c r="S3" t="b">
+        <v>1</v>
+      </c>
+      <c r="T3" t="n">
+        <v>3</v>
+      </c>
+      <c r="U3" t="n">
+        <v>2</v>
       </c>
     </row>
     <row r="4">
@@ -648,19 +695,19 @@
         <v>8.300000000000001</v>
       </c>
       <c r="G4" s="1" t="n">
-        <v>44645.38541666666</v>
+        <v>44645.55208333334</v>
       </c>
       <c r="H4" t="n">
-        <v>34.35</v>
+        <v>34.05</v>
       </c>
       <c r="I4" t="n">
         <v>34.25168832670541</v>
       </c>
       <c r="J4" s="2" t="n">
-        <v>15.83333333333333</v>
+        <v>16</v>
       </c>
       <c r="K4" t="n">
-        <v>6.51</v>
+        <v>5.58</v>
       </c>
       <c r="L4" t="n">
         <v>2.48</v>
@@ -678,7 +725,19 @@
         <v>1</v>
       </c>
       <c r="Q4" t="n">
-        <v>22</v>
+        <v>23</v>
+      </c>
+      <c r="R4" s="3" t="n">
+        <v>44651</v>
+      </c>
+      <c r="S4" t="b">
+        <v>0</v>
+      </c>
+      <c r="T4" t="n">
+        <v>1</v>
+      </c>
+      <c r="U4" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="5">
@@ -705,19 +764,19 @@
         <v>6.21</v>
       </c>
       <c r="G5" s="1" t="n">
-        <v>44664.38541666666</v>
+        <v>44664.55208333334</v>
       </c>
       <c r="H5" t="n">
-        <v>34.85</v>
+        <v>34.9</v>
       </c>
       <c r="I5" t="n">
         <v>34.87062362589548</v>
       </c>
       <c r="J5" s="2" t="n">
-        <v>18.83333333333333</v>
+        <v>19</v>
       </c>
       <c r="K5" t="n">
-        <v>-2.35</v>
+        <v>-2.5</v>
       </c>
       <c r="L5" t="n">
         <v>4.55</v>
@@ -735,7 +794,19 @@
         <v>0</v>
       </c>
       <c r="Q5" t="n">
-        <v>26</v>
+        <v>27</v>
+      </c>
+      <c r="R5" s="3" t="n">
+        <v>44651</v>
+      </c>
+      <c r="S5" t="b">
+        <v>1</v>
+      </c>
+      <c r="T5" t="n">
+        <v>2</v>
+      </c>
+      <c r="U5" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="6">
@@ -762,22 +833,22 @@
         <v>4.73</v>
       </c>
       <c r="G6" s="1" t="n">
-        <v>44680.55208333334</v>
+        <v>44683.38541666666</v>
       </c>
       <c r="H6" t="n">
-        <v>33.8</v>
+        <v>33.4</v>
       </c>
       <c r="I6" t="n">
         <v>33.59232049675611</v>
       </c>
       <c r="J6" s="2" t="n">
-        <v>16</v>
+        <v>18.83333333333333</v>
       </c>
       <c r="K6" t="n">
-        <v>-3.15</v>
+        <v>-4.3</v>
       </c>
       <c r="L6" t="n">
-        <v>4.01</v>
+        <v>5.01</v>
       </c>
       <c r="M6" t="n">
         <v>1.81</v>
@@ -792,7 +863,19 @@
         <v>0</v>
       </c>
       <c r="Q6" t="n">
-        <v>21</v>
+        <v>22</v>
+      </c>
+      <c r="R6" s="3" t="n">
+        <v>44679</v>
+      </c>
+      <c r="S6" t="b">
+        <v>1</v>
+      </c>
+      <c r="T6" t="n">
+        <v>2</v>
+      </c>
+      <c r="U6" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="7">
@@ -819,25 +902,25 @@
         <v>6.27</v>
       </c>
       <c r="G7" s="1" t="n">
-        <v>44711.55208333334</v>
+        <v>44712.38541666666</v>
       </c>
       <c r="H7" t="n">
-        <v>32.45</v>
+        <v>32.65</v>
       </c>
       <c r="I7" t="n">
         <v>32.6066350495804</v>
       </c>
       <c r="J7" s="2" t="n">
-        <v>28.16666666666667</v>
+        <v>29</v>
       </c>
       <c r="K7" t="n">
-        <v>2.84</v>
+        <v>2.25</v>
       </c>
       <c r="L7" t="n">
         <v>1.5</v>
       </c>
       <c r="M7" t="n">
-        <v>1.27</v>
+        <v>1.69</v>
       </c>
       <c r="N7" t="n">
         <v>3.04</v>
@@ -849,7 +932,19 @@
         <v>0</v>
       </c>
       <c r="Q7" t="n">
-        <v>40</v>
+        <v>41</v>
+      </c>
+      <c r="R7" s="3" t="n">
+        <v>44707</v>
+      </c>
+      <c r="S7" t="b">
+        <v>1</v>
+      </c>
+      <c r="T7" t="n">
+        <v>2</v>
+      </c>
+      <c r="U7" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="8">
@@ -876,28 +971,28 @@
         <v>5.05</v>
       </c>
       <c r="G8" s="1" t="n">
-        <v>44722.55208333334</v>
+        <v>44725.38541666666</v>
       </c>
       <c r="H8" t="n">
-        <v>32.15</v>
+        <v>30.6</v>
       </c>
       <c r="I8" t="n">
         <v>31.62259186894702</v>
       </c>
       <c r="J8" s="2" t="n">
-        <v>10.16666666666667</v>
+        <v>13</v>
       </c>
       <c r="K8" t="n">
-        <v>-1.53</v>
+        <v>-6.28</v>
       </c>
       <c r="L8" t="n">
-        <v>3.68</v>
+        <v>6.58</v>
       </c>
       <c r="M8" t="n">
-        <v>0.9399999999999999</v>
+        <v>2.02</v>
       </c>
       <c r="N8" t="n">
-        <v>2.11</v>
+        <v>4.67</v>
       </c>
       <c r="O8" t="n">
         <v>-0.15</v>
@@ -906,7 +1001,19 @@
         <v>0</v>
       </c>
       <c r="Q8" t="n">
-        <v>18</v>
+        <v>19</v>
+      </c>
+      <c r="R8" s="3" t="n">
+        <v>44742</v>
+      </c>
+      <c r="S8" t="b">
+        <v>0</v>
+      </c>
+      <c r="T8" t="n">
+        <v>1</v>
+      </c>
+      <c r="U8" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="9">
@@ -933,19 +1040,19 @@
         <v>7.14</v>
       </c>
       <c r="G9" s="1" t="n">
-        <v>44750.38541666666</v>
+        <v>44750.55208333334</v>
       </c>
       <c r="H9" t="n">
-        <v>30.9</v>
+        <v>31</v>
       </c>
       <c r="I9" t="n">
         <v>30.94377707102515</v>
       </c>
       <c r="J9" s="2" t="n">
-        <v>25</v>
+        <v>25.16666666666667</v>
       </c>
       <c r="K9" t="n">
-        <v>-0.98</v>
+        <v>-1.31</v>
       </c>
       <c r="L9" t="n">
         <v>2.94</v>
@@ -963,7 +1070,19 @@
         <v>1</v>
       </c>
       <c r="Q9" t="n">
-        <v>39</v>
+        <v>40</v>
+      </c>
+      <c r="R9" s="3" t="n">
+        <v>44742</v>
+      </c>
+      <c r="S9" t="b">
+        <v>1</v>
+      </c>
+      <c r="T9" t="n">
+        <v>2</v>
+      </c>
+      <c r="U9" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="10">
@@ -990,19 +1109,19 @@
         <v>4.01</v>
       </c>
       <c r="G10" s="1" t="n">
-        <v>44830.38541666666</v>
+        <v>44830.55208333334</v>
       </c>
       <c r="H10" t="n">
-        <v>33.85</v>
+        <v>33.7</v>
       </c>
       <c r="I10" t="n">
         <v>33.82296197744973</v>
       </c>
       <c r="J10" s="2" t="n">
-        <v>79.83333333333333</v>
+        <v>80</v>
       </c>
       <c r="K10" t="n">
-        <v>9.19</v>
+        <v>8.710000000000001</v>
       </c>
       <c r="L10" t="n">
         <v>2.26</v>
@@ -1020,7 +1139,19 @@
         <v>0</v>
       </c>
       <c r="Q10" t="n">
-        <v>106</v>
+        <v>107</v>
+      </c>
+      <c r="R10" s="3" t="n">
+        <v>44770</v>
+      </c>
+      <c r="S10" t="b">
+        <v>1</v>
+      </c>
+      <c r="T10" t="n">
+        <v>3</v>
+      </c>
+      <c r="U10" t="n">
+        <v>3</v>
       </c>
     </row>
     <row r="11">
@@ -1047,28 +1178,28 @@
         <v>7.43</v>
       </c>
       <c r="G11" s="1" t="n">
-        <v>44834.55208333334</v>
+        <v>44837.38541666666</v>
       </c>
       <c r="H11" t="n">
-        <v>33.8</v>
+        <v>36.35</v>
       </c>
       <c r="I11" t="n">
         <v>35.36304860224622</v>
       </c>
       <c r="J11" s="2" t="n">
-        <v>4</v>
+        <v>6.833333333333333</v>
       </c>
       <c r="K11" t="n">
-        <v>-0.3</v>
+        <v>-7.86</v>
       </c>
       <c r="L11" t="n">
-        <v>1.63</v>
+        <v>8.16</v>
       </c>
       <c r="M11" t="n">
         <v>0.75</v>
       </c>
       <c r="N11" t="n">
-        <v>2.74</v>
+        <v>5.62</v>
       </c>
       <c r="O11" t="n">
         <v>-4.13</v>
@@ -1077,7 +1208,19 @@
         <v>1</v>
       </c>
       <c r="Q11" t="n">
-        <v>9</v>
+        <v>10</v>
+      </c>
+      <c r="R11" s="3" t="n">
+        <v>44833</v>
+      </c>
+      <c r="S11" t="b">
+        <v>1</v>
+      </c>
+      <c r="T11" t="n">
+        <v>2</v>
+      </c>
+      <c r="U11" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="12">
@@ -1104,19 +1247,19 @@
         <v>11.12</v>
       </c>
       <c r="G12" s="1" t="n">
-        <v>44903.55208333334</v>
+        <v>44904.38541666666</v>
       </c>
       <c r="H12" t="n">
-        <v>70.59999999999999</v>
+        <v>67.90000000000001</v>
       </c>
       <c r="I12" t="n">
         <v>68.70858284747052</v>
       </c>
       <c r="J12" s="2" t="n">
-        <v>66.16666666666667</v>
+        <v>67</v>
       </c>
       <c r="K12" t="n">
-        <v>94.22</v>
+        <v>86.8</v>
       </c>
       <c r="L12" t="n">
         <v>6.74</v>
@@ -1134,7 +1277,19 @@
         <v>1</v>
       </c>
       <c r="Q12" t="n">
-        <v>91</v>
+        <v>92</v>
+      </c>
+      <c r="R12" s="3" t="n">
+        <v>44861</v>
+      </c>
+      <c r="S12" t="b">
+        <v>1</v>
+      </c>
+      <c r="T12" t="n">
+        <v>3</v>
+      </c>
+      <c r="U12" t="n">
+        <v>2</v>
       </c>
     </row>
     <row r="13">
@@ -1161,19 +1316,19 @@
         <v>14.61</v>
       </c>
       <c r="G13" s="1" t="n">
-        <v>44928.55208333334</v>
+        <v>44929.38541666666</v>
       </c>
       <c r="H13" t="n">
-        <v>68.7</v>
+        <v>71.95</v>
       </c>
       <c r="I13" t="n">
         <v>69.4945966349697</v>
       </c>
       <c r="J13" s="2" t="n">
-        <v>24.16666666666667</v>
+        <v>25</v>
       </c>
       <c r="K13" t="n">
-        <v>-1.18</v>
+        <v>-5.96</v>
       </c>
       <c r="L13" t="n">
         <v>11.41</v>
@@ -1191,7 +1346,19 @@
         <v>1</v>
       </c>
       <c r="Q13" t="n">
-        <v>34</v>
+        <v>35</v>
+      </c>
+      <c r="R13" s="3" t="n">
+        <v>44924</v>
+      </c>
+      <c r="S13" t="b">
+        <v>1</v>
+      </c>
+      <c r="T13" t="n">
+        <v>2</v>
+      </c>
+      <c r="U13" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="14">
@@ -1218,19 +1385,19 @@
         <v>10.46</v>
       </c>
       <c r="G14" s="1" t="n">
-        <v>44951.55208333334</v>
+        <v>44953.38541666666</v>
       </c>
       <c r="H14" t="n">
-        <v>75.8</v>
+        <v>72.15000000000001</v>
       </c>
       <c r="I14" t="n">
         <v>74.13743316511071</v>
       </c>
       <c r="J14" s="2" t="n">
-        <v>22.16666666666667</v>
+        <v>24</v>
       </c>
       <c r="K14" t="n">
-        <v>5.35</v>
+        <v>0.28</v>
       </c>
       <c r="L14" t="n">
         <v>3.89</v>
@@ -1248,7 +1415,19 @@
         <v>1</v>
       </c>
       <c r="Q14" t="n">
-        <v>34</v>
+        <v>35</v>
+      </c>
+      <c r="R14" s="3" t="n">
+        <v>44951</v>
+      </c>
+      <c r="S14" t="b">
+        <v>1</v>
+      </c>
+      <c r="T14" t="n">
+        <v>2</v>
+      </c>
+      <c r="U14" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="15">
@@ -1275,19 +1454,19 @@
         <v>11.19</v>
       </c>
       <c r="G15" s="1" t="n">
-        <v>44986.55208333334</v>
+        <v>44987.38541666666</v>
       </c>
       <c r="H15" t="n">
-        <v>58.65</v>
+        <v>66.2</v>
       </c>
       <c r="I15" t="n">
         <v>64.15086547353063</v>
       </c>
       <c r="J15" s="2" t="n">
-        <v>33.16666666666666</v>
+        <v>34</v>
       </c>
       <c r="K15" t="n">
-        <v>18.71</v>
+        <v>8.25</v>
       </c>
       <c r="L15" t="n">
         <v>9.98</v>
@@ -1296,7 +1475,7 @@
         <v>7.37</v>
       </c>
       <c r="N15" t="n">
-        <v>4.97</v>
+        <v>12.02</v>
       </c>
       <c r="O15" t="n">
         <v>-3.3</v>
@@ -1305,7 +1484,19 @@
         <v>0</v>
       </c>
       <c r="Q15" t="n">
-        <v>46</v>
+        <v>47</v>
+      </c>
+      <c r="R15" s="3" t="n">
+        <v>44980</v>
+      </c>
+      <c r="S15" t="b">
+        <v>1</v>
+      </c>
+      <c r="T15" t="n">
+        <v>2</v>
+      </c>
+      <c r="U15" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="16">
@@ -1332,19 +1523,19 @@
         <v>14.47</v>
       </c>
       <c r="G16" s="1" t="n">
-        <v>45061.55208333334</v>
+        <v>45062.38541666666</v>
       </c>
       <c r="H16" t="n">
-        <v>120.75</v>
+        <v>118.6</v>
       </c>
       <c r="I16" t="n">
         <v>118.9170378505208</v>
       </c>
       <c r="J16" s="2" t="n">
-        <v>74.16666666666667</v>
+        <v>75</v>
       </c>
       <c r="K16" t="n">
-        <v>82.40000000000001</v>
+        <v>79.15000000000001</v>
       </c>
       <c r="L16" t="n">
         <v>8.91</v>
@@ -1362,7 +1553,19 @@
         <v>1</v>
       </c>
       <c r="Q16" t="n">
-        <v>94</v>
+        <v>95</v>
+      </c>
+      <c r="R16" s="3" t="n">
+        <v>45014</v>
+      </c>
+      <c r="S16" t="b">
+        <v>1</v>
+      </c>
+      <c r="T16" t="n">
+        <v>3</v>
+      </c>
+      <c r="U16" t="n">
+        <v>3</v>
       </c>
     </row>
     <row r="17">
@@ -1389,28 +1592,28 @@
         <v>14.26</v>
       </c>
       <c r="G17" s="1" t="n">
-        <v>45083.55208333334</v>
+        <v>45084.38541666666</v>
       </c>
       <c r="H17" t="n">
-        <v>119.6</v>
+        <v>128.15</v>
       </c>
       <c r="I17" t="n">
         <v>123.5166300848938</v>
       </c>
       <c r="J17" s="2" t="n">
-        <v>21.16666666666667</v>
+        <v>22</v>
       </c>
       <c r="K17" t="n">
-        <v>-0.84</v>
+        <v>-8.050000000000001</v>
       </c>
       <c r="L17" t="n">
-        <v>4.89</v>
+        <v>11.38</v>
       </c>
       <c r="M17" t="n">
-        <v>1.44</v>
+        <v>1.51</v>
       </c>
       <c r="N17" t="n">
-        <v>4.98</v>
+        <v>6.02</v>
       </c>
       <c r="O17" t="n">
         <v>-1.53</v>
@@ -1419,7 +1622,19 @@
         <v>0</v>
       </c>
       <c r="Q17" t="n">
-        <v>32</v>
+        <v>33</v>
+      </c>
+      <c r="R17" s="3" t="n">
+        <v>45071</v>
+      </c>
+      <c r="S17" t="b">
+        <v>1</v>
+      </c>
+      <c r="T17" t="n">
+        <v>2</v>
+      </c>
+      <c r="U17" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="18">
@@ -1446,19 +1661,19 @@
         <v>10.93</v>
       </c>
       <c r="G18" s="1" t="n">
-        <v>45131.55208333334</v>
+        <v>45132.38541666666</v>
       </c>
       <c r="H18" t="n">
-        <v>133.9</v>
+        <v>130.65</v>
       </c>
       <c r="I18" t="n">
         <v>131.1674933852626</v>
       </c>
       <c r="J18" s="2" t="n">
-        <v>47.16666666666666</v>
+        <v>48</v>
       </c>
       <c r="K18" t="n">
-        <v>4.49</v>
+        <v>1.95</v>
       </c>
       <c r="L18" t="n">
         <v>8.66</v>
@@ -1476,7 +1691,19 @@
         <v>1</v>
       </c>
       <c r="Q18" t="n">
-        <v>66</v>
+        <v>67</v>
+      </c>
+      <c r="R18" s="3" t="n">
+        <v>45105</v>
+      </c>
+      <c r="S18" t="b">
+        <v>1</v>
+      </c>
+      <c r="T18" t="n">
+        <v>2</v>
+      </c>
+      <c r="U18" t="n">
+        <v>2</v>
       </c>
     </row>
     <row r="19">
@@ -1503,19 +1730,19 @@
         <v>12.1</v>
       </c>
       <c r="G19" s="1" t="n">
-        <v>45166.55208333334</v>
+        <v>45167.38541666666</v>
       </c>
       <c r="H19" t="n">
-        <v>127.8</v>
+        <v>130.85</v>
       </c>
       <c r="I19" t="n">
         <v>129.3737311413596</v>
       </c>
       <c r="J19" s="2" t="n">
-        <v>34.16666666666666</v>
+        <v>35</v>
       </c>
       <c r="K19" t="n">
-        <v>2.18</v>
+        <v>-0.15</v>
       </c>
       <c r="L19" t="n">
         <v>3.75</v>
@@ -1533,7 +1760,19 @@
         <v>0</v>
       </c>
       <c r="Q19" t="n">
-        <v>48</v>
+        <v>49</v>
+      </c>
+      <c r="R19" s="3" t="n">
+        <v>45134</v>
+      </c>
+      <c r="S19" t="b">
+        <v>1</v>
+      </c>
+      <c r="T19" t="n">
+        <v>2</v>
+      </c>
+      <c r="U19" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="20">
@@ -1560,19 +1799,19 @@
         <v>5.87</v>
       </c>
       <c r="G20" s="1" t="n">
-        <v>45189.55208333334</v>
+        <v>45190.38541666666</v>
       </c>
       <c r="H20" t="n">
-        <v>163.65</v>
+        <v>160.25</v>
       </c>
       <c r="I20" t="n">
         <v>163.047899237656</v>
       </c>
       <c r="J20" s="2" t="n">
-        <v>22.16666666666667</v>
+        <v>23</v>
       </c>
       <c r="K20" t="n">
-        <v>25.07</v>
+        <v>22.47</v>
       </c>
       <c r="L20" t="n">
         <v>2.83</v>
@@ -1590,7 +1829,19 @@
         <v>0</v>
       </c>
       <c r="Q20" t="n">
-        <v>32</v>
+        <v>33</v>
+      </c>
+      <c r="R20" s="3" t="n">
+        <v>45169</v>
+      </c>
+      <c r="S20" t="b">
+        <v>1</v>
+      </c>
+      <c r="T20" t="n">
+        <v>2</v>
+      </c>
+      <c r="U20" t="n">
+        <v>2</v>
       </c>
     </row>
     <row r="21">
@@ -1617,19 +1868,19 @@
         <v>14.78</v>
       </c>
       <c r="G21" s="1" t="n">
-        <v>45246.55208333334</v>
+        <v>45247.38541666666</v>
       </c>
       <c r="H21" t="n">
-        <v>158.65</v>
+        <v>167.5</v>
       </c>
       <c r="I21" t="n">
         <v>162.9368546279034</v>
       </c>
       <c r="J21" s="2" t="n">
-        <v>56.16666666666666</v>
+        <v>57</v>
       </c>
       <c r="K21" t="n">
-        <v>1</v>
+        <v>-4.52</v>
       </c>
       <c r="L21" t="n">
         <v>10.39</v>
@@ -1638,7 +1889,7 @@
         <v>3.25</v>
       </c>
       <c r="N21" t="n">
-        <v>4.68</v>
+        <v>4.85</v>
       </c>
       <c r="O21" t="n">
         <v>-2.75</v>
@@ -1647,7 +1898,19 @@
         <v>0</v>
       </c>
       <c r="Q21" t="n">
-        <v>77</v>
+        <v>78</v>
+      </c>
+      <c r="R21" s="3" t="n">
+        <v>45197</v>
+      </c>
+      <c r="S21" t="b">
+        <v>1</v>
+      </c>
+      <c r="T21" t="n">
+        <v>3</v>
+      </c>
+      <c r="U21" t="n">
+        <v>2</v>
       </c>
     </row>
     <row r="22">
@@ -1674,19 +1937,19 @@
         <v>8.92</v>
       </c>
       <c r="G22" s="1" t="n">
-        <v>45280.38541666666</v>
+        <v>45280.55208333334</v>
       </c>
       <c r="H22" t="n">
-        <v>182.1</v>
+        <v>172.4</v>
       </c>
       <c r="I22" t="n">
         <v>172.5374074141561</v>
       </c>
       <c r="J22" s="2" t="n">
-        <v>33</v>
+        <v>33.16666666666666</v>
       </c>
       <c r="K22" t="n">
-        <v>8.720000000000001</v>
+        <v>2.93</v>
       </c>
       <c r="L22" t="n">
         <v>5.61</v>
@@ -1704,7 +1967,19 @@
         <v>1</v>
       </c>
       <c r="Q22" t="n">
-        <v>45</v>
+        <v>46</v>
+      </c>
+      <c r="R22" s="3" t="n">
+        <v>45260</v>
+      </c>
+      <c r="S22" t="b">
+        <v>1</v>
+      </c>
+      <c r="T22" t="n">
+        <v>2</v>
+      </c>
+      <c r="U22" t="n">
+        <v>2</v>
       </c>
     </row>
     <row r="23">
@@ -1731,25 +2006,25 @@
         <v>10.81</v>
       </c>
       <c r="G23" s="1" t="n">
-        <v>45293.55208333334</v>
+        <v>45294.38541666666</v>
       </c>
       <c r="H23" t="n">
-        <v>181.15</v>
+        <v>187.85</v>
       </c>
       <c r="I23" t="n">
         <v>187.8055144955722</v>
       </c>
       <c r="J23" s="2" t="n">
-        <v>13</v>
+        <v>13.83333333333333</v>
       </c>
       <c r="K23" t="n">
-        <v>-5.08</v>
+        <v>-8.960000000000001</v>
       </c>
       <c r="L23" t="n">
-        <v>7.66</v>
+        <v>9.050000000000001</v>
       </c>
       <c r="M23" t="n">
-        <v>0.54</v>
+        <v>0.97</v>
       </c>
       <c r="N23" t="n">
         <v>3.19</v>
@@ -1761,7 +2036,19 @@
         <v>1</v>
       </c>
       <c r="Q23" t="n">
-        <v>17</v>
+        <v>18</v>
+      </c>
+      <c r="R23" s="3" t="n">
+        <v>45288</v>
+      </c>
+      <c r="S23" t="b">
+        <v>1</v>
+      </c>
+      <c r="T23" t="n">
+        <v>2</v>
+      </c>
+      <c r="U23" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="24">
@@ -1788,25 +2075,25 @@
         <v>7.85</v>
       </c>
       <c r="G24" s="1" t="n">
-        <v>45330.55208333334</v>
+        <v>45331.38541666666</v>
       </c>
       <c r="H24" t="n">
-        <v>281.2</v>
+        <v>258.85</v>
       </c>
       <c r="I24" t="n">
         <v>279.1669343332765</v>
       </c>
       <c r="J24" s="2" t="n">
-        <v>36.16666666666666</v>
+        <v>37</v>
       </c>
       <c r="K24" t="n">
-        <v>49.69</v>
+        <v>37.8</v>
       </c>
       <c r="L24" t="n">
         <v>3.49</v>
       </c>
       <c r="M24" t="n">
-        <v>0.47</v>
+        <v>8.25</v>
       </c>
       <c r="N24" t="n">
         <v>9.94</v>
@@ -1818,7 +2105,19 @@
         <v>0</v>
       </c>
       <c r="Q24" t="n">
-        <v>52</v>
+        <v>53</v>
+      </c>
+      <c r="R24" s="3" t="n">
+        <v>45316</v>
+      </c>
+      <c r="S24" t="b">
+        <v>1</v>
+      </c>
+      <c r="T24" t="n">
+        <v>2</v>
+      </c>
+      <c r="U24" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="25">
@@ -1845,19 +2144,19 @@
         <v>15.92</v>
       </c>
       <c r="G25" s="1" t="n">
-        <v>45373.55208333334</v>
+        <v>45377.38541666666</v>
       </c>
       <c r="H25" t="n">
-        <v>249.15</v>
+        <v>262.4</v>
       </c>
       <c r="I25" t="n">
         <v>253.8238896916103</v>
       </c>
       <c r="J25" s="2" t="n">
-        <v>42.16666666666666</v>
+        <v>46</v>
       </c>
       <c r="K25" t="n">
-        <v>3.75</v>
+        <v>-1.37</v>
       </c>
       <c r="L25" t="n">
         <v>8.67</v>
@@ -1875,7 +2174,19 @@
         <v>1</v>
       </c>
       <c r="Q25" t="n">
-        <v>59</v>
+        <v>60</v>
+      </c>
+      <c r="R25" s="3" t="n">
+        <v>45351</v>
+      </c>
+      <c r="S25" t="b">
+        <v>1</v>
+      </c>
+      <c r="T25" t="n">
+        <v>2</v>
+      </c>
+      <c r="U25" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="26">
@@ -1902,19 +2213,19 @@
         <v>11.54</v>
       </c>
       <c r="G26" s="1" t="n">
-        <v>45418.55208333334</v>
+        <v>45419.38541666666</v>
       </c>
       <c r="H26" t="n">
-        <v>275.5</v>
+        <v>265.15</v>
       </c>
       <c r="I26" t="n">
         <v>272.0659815284799</v>
       </c>
       <c r="J26" s="2" t="n">
-        <v>41.16666666666666</v>
+        <v>42</v>
       </c>
       <c r="K26" t="n">
-        <v>4.99</v>
+        <v>1.05</v>
       </c>
       <c r="L26" t="n">
         <v>6.63</v>
@@ -1932,7 +2243,19 @@
         <v>1</v>
       </c>
       <c r="Q26" t="n">
-        <v>52</v>
+        <v>53</v>
+      </c>
+      <c r="R26" s="3" t="n">
+        <v>45379</v>
+      </c>
+      <c r="S26" t="b">
+        <v>1</v>
+      </c>
+      <c r="T26" t="n">
+        <v>3</v>
+      </c>
+      <c r="U26" t="n">
+        <v>2</v>
       </c>
     </row>
     <row r="27">
@@ -1959,22 +2282,22 @@
         <v>9.98</v>
       </c>
       <c r="G27" s="1" t="n">
-        <v>45427.55208333334</v>
+        <v>45428.38541666666</v>
       </c>
       <c r="H27" t="n">
-        <v>275.8</v>
+        <v>279.4</v>
       </c>
       <c r="I27" t="n">
         <v>278.3175276335807</v>
       </c>
       <c r="J27" s="2" t="n">
-        <v>8.166666666666666</v>
+        <v>9</v>
       </c>
       <c r="K27" t="n">
-        <v>-4.02</v>
+        <v>-5.37</v>
       </c>
       <c r="L27" t="n">
-        <v>4.85</v>
+        <v>7.17</v>
       </c>
       <c r="M27" t="n">
         <v>1.48</v>
@@ -1989,7 +2312,19 @@
         <v>0</v>
       </c>
       <c r="Q27" t="n">
-        <v>14</v>
+        <v>15</v>
+      </c>
+      <c r="R27" s="3" t="n">
+        <v>45442</v>
+      </c>
+      <c r="S27" t="b">
+        <v>0</v>
+      </c>
+      <c r="T27" t="n">
+        <v>1</v>
+      </c>
+      <c r="U27" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="28">
@@ -2016,28 +2351,28 @@
         <v>8.09</v>
       </c>
       <c r="G28" s="1" t="n">
-        <v>45446.55208333334</v>
+        <v>45447.38541666666</v>
       </c>
       <c r="H28" t="n">
-        <v>404.8</v>
+        <v>357.75</v>
       </c>
       <c r="I28" t="n">
         <v>361.8978781320285</v>
       </c>
       <c r="J28" s="2" t="n">
-        <v>18.16666666666667</v>
+        <v>19</v>
       </c>
       <c r="K28" t="n">
-        <v>44.88</v>
+        <v>28.04</v>
       </c>
       <c r="L28" t="n">
         <v>1.25</v>
       </c>
       <c r="M28" t="n">
-        <v>0.5600000000000001</v>
+        <v>1.19</v>
       </c>
       <c r="N28" t="n">
-        <v>1.29</v>
+        <v>13.22</v>
       </c>
       <c r="O28" t="n">
         <v>1.81</v>
@@ -2046,7 +2381,19 @@
         <v>0</v>
       </c>
       <c r="Q28" t="n">
-        <v>25</v>
+        <v>26</v>
+      </c>
+      <c r="R28" s="3" t="n">
+        <v>45442</v>
+      </c>
+      <c r="S28" t="b">
+        <v>1</v>
+      </c>
+      <c r="T28" t="n">
+        <v>2</v>
+      </c>
+      <c r="U28" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="29">
@@ -2073,22 +2420,22 @@
         <v>18.83</v>
       </c>
       <c r="G29" s="1" t="n">
-        <v>45464.55208333334</v>
+        <v>45467.38541666666</v>
       </c>
       <c r="H29" t="n">
-        <v>409.5</v>
+        <v>418.6</v>
       </c>
       <c r="I29" t="n">
         <v>416.7703204092452</v>
       </c>
       <c r="J29" s="2" t="n">
-        <v>17.16666666666667</v>
+        <v>20</v>
       </c>
       <c r="K29" t="n">
-        <v>-14.47</v>
+        <v>-17.01</v>
       </c>
       <c r="L29" t="n">
-        <v>16.67</v>
+        <v>20.7</v>
       </c>
       <c r="M29" t="n">
         <v>4.51</v>
@@ -2103,7 +2450,19 @@
         <v>1</v>
       </c>
       <c r="Q29" t="n">
-        <v>26</v>
+        <v>27</v>
+      </c>
+      <c r="R29" s="3" t="n">
+        <v>45470</v>
+      </c>
+      <c r="S29" t="b">
+        <v>0</v>
+      </c>
+      <c r="T29" t="n">
+        <v>1</v>
+      </c>
+      <c r="U29" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="30">
@@ -2130,28 +2489,28 @@
         <v>9.460000000000001</v>
       </c>
       <c r="G30" s="1" t="n">
-        <v>45506.55208333334</v>
+        <v>45509.38541666666</v>
       </c>
       <c r="H30" t="n">
-        <v>588.5</v>
+        <v>551.4</v>
       </c>
       <c r="I30" t="n">
         <v>553.259959241005</v>
       </c>
       <c r="J30" s="2" t="n">
-        <v>39.16666666666666</v>
+        <v>42</v>
       </c>
       <c r="K30" t="n">
-        <v>40.59</v>
+        <v>31.72</v>
       </c>
       <c r="L30" t="n">
         <v>4.12</v>
       </c>
       <c r="M30" t="n">
-        <v>2.54</v>
+        <v>4.88</v>
       </c>
       <c r="N30" t="n">
-        <v>6.04</v>
+        <v>6.47</v>
       </c>
       <c r="O30" t="n">
         <v>1.83</v>
@@ -2160,7 +2519,19 @@
         <v>0</v>
       </c>
       <c r="Q30" t="n">
-        <v>58</v>
+        <v>59</v>
+      </c>
+      <c r="R30" s="3" t="n">
+        <v>45470</v>
+      </c>
+      <c r="S30" t="b">
+        <v>1</v>
+      </c>
+      <c r="T30" t="n">
+        <v>3</v>
+      </c>
+      <c r="U30" t="n">
+        <v>2</v>
       </c>
     </row>
     <row r="31">
@@ -2187,22 +2558,22 @@
         <v>12.29</v>
       </c>
       <c r="G31" s="1" t="n">
-        <v>45533.55208333334</v>
+        <v>45534.38541666666</v>
       </c>
       <c r="H31" t="n">
-        <v>578.3</v>
+        <v>602.85</v>
       </c>
       <c r="I31" t="n">
         <v>582.8021446100365</v>
       </c>
       <c r="J31" s="2" t="n">
-        <v>24.16666666666667</v>
+        <v>25</v>
       </c>
       <c r="K31" t="n">
-        <v>-4.88</v>
+        <v>-9.33</v>
       </c>
       <c r="L31" t="n">
-        <v>9.16</v>
+        <v>9.720000000000001</v>
       </c>
       <c r="M31" t="n">
         <v>3.35</v>
@@ -2217,7 +2588,19 @@
         <v>1</v>
       </c>
       <c r="Q31" t="n">
-        <v>36</v>
+        <v>37</v>
+      </c>
+      <c r="R31" s="3" t="n">
+        <v>45533</v>
+      </c>
+      <c r="S31" t="b">
+        <v>1</v>
+      </c>
+      <c r="T31" t="n">
+        <v>2</v>
+      </c>
+      <c r="U31" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="32">
@@ -2244,25 +2627,25 @@
         <v>8.41</v>
       </c>
       <c r="G32" s="1" t="n">
-        <v>45541.55208333334</v>
+        <v>45544.38541666666</v>
       </c>
       <c r="H32" t="n">
-        <v>572</v>
+        <v>557.25</v>
       </c>
       <c r="I32" t="n">
         <v>565.288230361833</v>
       </c>
       <c r="J32" s="2" t="n">
-        <v>7.166666666666667</v>
+        <v>10</v>
       </c>
       <c r="K32" t="n">
-        <v>-5.12</v>
+        <v>-7.56</v>
       </c>
       <c r="L32" t="n">
-        <v>6.2</v>
+        <v>8.210000000000001</v>
       </c>
       <c r="M32" t="n">
-        <v>0.22</v>
+        <v>0.43</v>
       </c>
       <c r="N32" t="n">
         <v>1.8</v>
@@ -2274,7 +2657,19 @@
         <v>1</v>
       </c>
       <c r="Q32" t="n">
-        <v>12</v>
+        <v>13</v>
+      </c>
+      <c r="R32" s="3" t="n">
+        <v>45561</v>
+      </c>
+      <c r="S32" t="b">
+        <v>0</v>
+      </c>
+      <c r="T32" t="n">
+        <v>1</v>
+      </c>
+      <c r="U32" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="33">
@@ -2301,19 +2696,19 @@
         <v>7.63</v>
       </c>
       <c r="G33" s="1" t="n">
-        <v>45555.38541666666</v>
+        <v>45555.55208333334</v>
       </c>
       <c r="H33" t="n">
-        <v>541.8</v>
+        <v>545</v>
       </c>
       <c r="I33" t="n">
         <v>543.225516889746</v>
       </c>
       <c r="J33" s="2" t="n">
-        <v>11</v>
+        <v>11.16666666666667</v>
       </c>
       <c r="K33" t="n">
-        <v>2.77</v>
+        <v>2.2</v>
       </c>
       <c r="L33" t="n">
         <v>3.87</v>
@@ -2331,7 +2726,19 @@
         <v>0</v>
       </c>
       <c r="Q33" t="n">
-        <v>19</v>
+        <v>20</v>
+      </c>
+      <c r="R33" s="3" t="n">
+        <v>45561</v>
+      </c>
+      <c r="S33" t="b">
+        <v>0</v>
+      </c>
+      <c r="T33" t="n">
+        <v>1</v>
+      </c>
+      <c r="U33" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="34">
@@ -2358,28 +2765,28 @@
         <v>8.69</v>
       </c>
       <c r="G34" s="1" t="n">
-        <v>45568.55208333334</v>
+        <v>45569.38541666666</v>
       </c>
       <c r="H34" t="n">
-        <v>509.7</v>
+        <v>496.15</v>
       </c>
       <c r="I34" t="n">
         <v>497.6190813193057</v>
       </c>
       <c r="J34" s="2" t="n">
-        <v>13</v>
+        <v>13.83333333333333</v>
       </c>
       <c r="K34" t="n">
-        <v>-6.48</v>
+        <v>-8.960000000000001</v>
       </c>
       <c r="L34" t="n">
-        <v>6.97</v>
+        <v>11.26</v>
       </c>
       <c r="M34" t="n">
         <v>2.64</v>
       </c>
       <c r="N34" t="n">
-        <v>2.88</v>
+        <v>2.9</v>
       </c>
       <c r="O34" t="n">
         <v>6.47</v>
@@ -2388,7 +2795,19 @@
         <v>1</v>
       </c>
       <c r="Q34" t="n">
-        <v>17</v>
+        <v>18</v>
+      </c>
+      <c r="R34" s="3" t="n">
+        <v>45561</v>
+      </c>
+      <c r="S34" t="b">
+        <v>1</v>
+      </c>
+      <c r="T34" t="n">
+        <v>2</v>
+      </c>
+      <c r="U34" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="35">
@@ -2415,19 +2834,19 @@
         <v>7.47</v>
       </c>
       <c r="G35" s="1" t="n">
-        <v>45594.55208333334</v>
+        <v>45595.38541666666</v>
       </c>
       <c r="H35" t="n">
-        <v>438.9</v>
+        <v>475.65</v>
       </c>
       <c r="I35" t="n">
         <v>463.7556228866286</v>
       </c>
       <c r="J35" s="2" t="n">
-        <v>25.16666666666667</v>
+        <v>26</v>
       </c>
       <c r="K35" t="n">
-        <v>11.54</v>
+        <v>4.13</v>
       </c>
       <c r="L35" t="n">
         <v>3.73</v>
@@ -2445,7 +2864,19 @@
         <v>0</v>
       </c>
       <c r="Q35" t="n">
-        <v>36</v>
+        <v>37</v>
+      </c>
+      <c r="R35" s="3" t="n">
+        <v>45596</v>
+      </c>
+      <c r="S35" t="b">
+        <v>0</v>
+      </c>
+      <c r="T35" t="n">
+        <v>1</v>
+      </c>
+      <c r="U35" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="36">
@@ -2472,22 +2903,22 @@
         <v>14.58</v>
       </c>
       <c r="G36" s="1" t="n">
-        <v>45604.55208333334</v>
+        <v>45607.38541666666</v>
       </c>
       <c r="H36" t="n">
-        <v>448</v>
+        <v>435.7</v>
       </c>
       <c r="I36" t="n">
         <v>437.115089295089</v>
       </c>
       <c r="J36" s="2" t="n">
-        <v>9.166666666666666</v>
+        <v>12</v>
       </c>
       <c r="K36" t="n">
-        <v>-5.81</v>
+        <v>-8.4</v>
       </c>
       <c r="L36" t="n">
-        <v>8.33</v>
+        <v>9.77</v>
       </c>
       <c r="M36" t="n">
         <v>6.75</v>
@@ -2502,7 +2933,19 @@
         <v>1</v>
       </c>
       <c r="Q36" t="n">
-        <v>15</v>
+        <v>16</v>
+      </c>
+      <c r="R36" s="3" t="n">
+        <v>45596</v>
+      </c>
+      <c r="S36" t="b">
+        <v>1</v>
+      </c>
+      <c r="T36" t="n">
+        <v>2</v>
+      </c>
+      <c r="U36" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="37">
@@ -2529,19 +2972,19 @@
         <v>11.1</v>
       </c>
       <c r="G37" s="1" t="n">
-        <v>45631.55208333334</v>
+        <v>45632.38541666666</v>
       </c>
       <c r="H37" t="n">
-        <v>443.4</v>
+        <v>456.35</v>
       </c>
       <c r="I37" t="n">
         <v>453.4165481303321</v>
       </c>
       <c r="J37" s="2" t="n">
-        <v>24.16666666666667</v>
+        <v>25</v>
       </c>
       <c r="K37" t="n">
-        <v>-1.77</v>
+        <v>-4.74</v>
       </c>
       <c r="L37" t="n">
         <v>6.24</v>
@@ -2550,7 +2993,7 @@
         <v>6.94</v>
       </c>
       <c r="N37" t="n">
-        <v>3.91</v>
+        <v>4.76</v>
       </c>
       <c r="O37" t="n">
         <v>-2.34</v>
@@ -2559,7 +3002,19 @@
         <v>0</v>
       </c>
       <c r="Q37" t="n">
-        <v>34</v>
+        <v>35</v>
+      </c>
+      <c r="R37" s="3" t="n">
+        <v>45624</v>
+      </c>
+      <c r="S37" t="b">
+        <v>1</v>
+      </c>
+      <c r="T37" t="n">
+        <v>2</v>
+      </c>
+      <c r="U37" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="38">
@@ -2586,19 +3041,19 @@
         <v>7.31</v>
       </c>
       <c r="G38" s="1" t="n">
-        <v>45645.55208333334</v>
+        <v>45646.38541666666</v>
       </c>
       <c r="H38" t="n">
-        <v>448.15</v>
+        <v>441.25</v>
       </c>
       <c r="I38" t="n">
         <v>445.6018930119536</v>
       </c>
       <c r="J38" s="2" t="n">
-        <v>13.16666666666667</v>
+        <v>14</v>
       </c>
       <c r="K38" t="n">
-        <v>-1.8</v>
+        <v>-3.31</v>
       </c>
       <c r="L38" t="n">
         <v>4.02</v>
@@ -2607,7 +3062,7 @@
         <v>4.65</v>
       </c>
       <c r="N38" t="n">
-        <v>2.55</v>
+        <v>3.36</v>
       </c>
       <c r="O38" t="n">
         <v>4.76</v>
@@ -2616,7 +3071,19 @@
         <v>1</v>
       </c>
       <c r="Q38" t="n">
-        <v>20</v>
+        <v>21</v>
+      </c>
+      <c r="R38" s="3" t="n">
+        <v>45652</v>
+      </c>
+      <c r="S38" t="b">
+        <v>0</v>
+      </c>
+      <c r="T38" t="n">
+        <v>1</v>
+      </c>
+      <c r="U38" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="39">
@@ -2643,28 +3110,28 @@
         <v>8.43</v>
       </c>
       <c r="G39" s="1" t="n">
-        <v>45672.55208333334</v>
+        <v>45673.38541666666</v>
       </c>
       <c r="H39" t="n">
-        <v>372.35</v>
+        <v>403.5</v>
       </c>
       <c r="I39" t="n">
         <v>393.5638020543238</v>
       </c>
       <c r="J39" s="2" t="n">
-        <v>26.16666666666667</v>
+        <v>27</v>
       </c>
       <c r="K39" t="n">
-        <v>15.61</v>
+        <v>8.56</v>
       </c>
       <c r="L39" t="n">
         <v>2.8</v>
       </c>
       <c r="M39" t="n">
-        <v>1.06</v>
+        <v>5.24</v>
       </c>
       <c r="N39" t="n">
-        <v>4.2</v>
+        <v>10.65</v>
       </c>
       <c r="O39" t="n">
         <v>-3.36</v>
@@ -2673,7 +3140,19 @@
         <v>0</v>
       </c>
       <c r="Q39" t="n">
-        <v>36</v>
+        <v>37</v>
+      </c>
+      <c r="R39" s="3" t="n">
+        <v>45652</v>
+      </c>
+      <c r="S39" t="b">
+        <v>1</v>
+      </c>
+      <c r="T39" t="n">
+        <v>2</v>
+      </c>
+      <c r="U39" t="n">
+        <v>2</v>
       </c>
     </row>
     <row r="40">
@@ -2700,25 +3179,25 @@
         <v>11.35</v>
       </c>
       <c r="G40" s="1" t="n">
-        <v>45689.55208333334</v>
+        <v>45691.38541666666</v>
       </c>
       <c r="H40" t="n">
-        <v>432</v>
+        <v>403.9</v>
       </c>
       <c r="I40" t="n">
         <v>422.4423603721448</v>
       </c>
       <c r="J40" s="2" t="n">
-        <v>16.16666666666667</v>
+        <v>18</v>
       </c>
       <c r="K40" t="n">
-        <v>7.06</v>
+        <v>0.1</v>
       </c>
       <c r="L40" t="n">
         <v>4.54</v>
       </c>
       <c r="M40" t="n">
-        <v>2.53</v>
+        <v>3.9</v>
       </c>
       <c r="N40" t="n">
         <v>9.619999999999999</v>
@@ -2730,7 +3209,19 @@
         <v>1</v>
       </c>
       <c r="Q40" t="n">
-        <v>26</v>
+        <v>27</v>
+      </c>
+      <c r="R40" s="3" t="n">
+        <v>45687</v>
+      </c>
+      <c r="S40" t="b">
+        <v>1</v>
+      </c>
+      <c r="T40" t="n">
+        <v>2</v>
+      </c>
+      <c r="U40" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="41">
@@ -2757,19 +3248,19 @@
         <v>18.2</v>
       </c>
       <c r="G41" s="1" t="n">
-        <v>45707.55208333334</v>
+        <v>45708.38541666666</v>
       </c>
       <c r="H41" t="n">
-        <v>373</v>
+        <v>380.1</v>
       </c>
       <c r="I41" t="n">
         <v>374.1161581682597</v>
       </c>
       <c r="J41" s="2" t="n">
-        <v>16.16666666666667</v>
+        <v>17</v>
       </c>
       <c r="K41" t="n">
-        <v>7.65</v>
+        <v>5.89</v>
       </c>
       <c r="L41" t="n">
         <v>4.31</v>
@@ -2787,7 +3278,19 @@
         <v>1</v>
       </c>
       <c r="Q41" t="n">
-        <v>26</v>
+        <v>27</v>
+      </c>
+      <c r="R41" s="3" t="n">
+        <v>45715</v>
+      </c>
+      <c r="S41" t="b">
+        <v>0</v>
+      </c>
+      <c r="T41" t="n">
+        <v>1</v>
+      </c>
+      <c r="U41" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="42">
@@ -2814,22 +3317,22 @@
         <v>16.5</v>
       </c>
       <c r="G42" s="1" t="n">
-        <v>45716.55208333334</v>
+        <v>45719.38541666666</v>
       </c>
       <c r="H42" t="n">
-        <v>332.45</v>
+        <v>327.2</v>
       </c>
       <c r="I42" t="n">
         <v>328.8563661258048</v>
       </c>
       <c r="J42" s="2" t="n">
-        <v>8.166666666666666</v>
+        <v>11</v>
       </c>
       <c r="K42" t="n">
-        <v>-12.54</v>
+        <v>-13.92</v>
       </c>
       <c r="L42" t="n">
-        <v>13.71</v>
+        <v>18.36</v>
       </c>
       <c r="M42" t="n">
         <v>1.22</v>
@@ -2844,7 +3347,19 @@
         <v>0</v>
       </c>
       <c r="Q42" t="n">
-        <v>12</v>
+        <v>13</v>
+      </c>
+      <c r="R42" s="3" t="n">
+        <v>45715</v>
+      </c>
+      <c r="S42" t="b">
+        <v>1</v>
+      </c>
+      <c r="T42" t="n">
+        <v>2</v>
+      </c>
+      <c r="U42" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="43">
@@ -2871,28 +3386,28 @@
         <v>13.61</v>
       </c>
       <c r="G43" s="1" t="n">
-        <v>45734.55208333334</v>
+        <v>45735.38541666666</v>
       </c>
       <c r="H43" t="n">
-        <v>333.6</v>
+        <v>361.95</v>
       </c>
       <c r="I43" t="n">
         <v>355.6015684811715</v>
       </c>
       <c r="J43" s="2" t="n">
-        <v>15.16666666666667</v>
+        <v>16</v>
       </c>
       <c r="K43" t="n">
-        <v>-1.96</v>
+        <v>-10.62</v>
       </c>
       <c r="L43" t="n">
-        <v>7.4</v>
+        <v>10.62</v>
       </c>
       <c r="M43" t="n">
         <v>2.11</v>
       </c>
       <c r="N43" t="n">
-        <v>2.82</v>
+        <v>6.12</v>
       </c>
       <c r="O43" t="n">
         <v>-2.02</v>
@@ -2901,7 +3416,19 @@
         <v>0</v>
       </c>
       <c r="Q43" t="n">
-        <v>22</v>
+        <v>23</v>
+      </c>
+      <c r="R43" s="3" t="n">
+        <v>45743</v>
+      </c>
+      <c r="S43" t="b">
+        <v>0</v>
+      </c>
+      <c r="T43" t="n">
+        <v>1</v>
+      </c>
+      <c r="U43" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="44">
@@ -2928,28 +3455,28 @@
         <v>12.52</v>
       </c>
       <c r="G44" s="1" t="n">
-        <v>45751.55208333334</v>
+        <v>45754.38541666666</v>
       </c>
       <c r="H44" t="n">
-        <v>351.4</v>
+        <v>327.3</v>
       </c>
       <c r="I44" t="n">
         <v>340.5180441932874</v>
       </c>
       <c r="J44" s="2" t="n">
-        <v>16.16666666666667</v>
+        <v>19</v>
       </c>
       <c r="K44" t="n">
-        <v>-2.91</v>
+        <v>-9.57</v>
       </c>
       <c r="L44" t="n">
-        <v>7.72</v>
+        <v>15.73</v>
       </c>
       <c r="M44" t="n">
-        <v>2.34</v>
+        <v>13.2</v>
       </c>
       <c r="N44" t="n">
-        <v>2.46</v>
+        <v>3.64</v>
       </c>
       <c r="O44" t="n">
         <v>6.12</v>
@@ -2958,7 +3485,19 @@
         <v>1</v>
       </c>
       <c r="Q44" t="n">
-        <v>22</v>
+        <v>23</v>
+      </c>
+      <c r="R44" s="3" t="n">
+        <v>45743</v>
+      </c>
+      <c r="S44" t="b">
+        <v>1</v>
+      </c>
+      <c r="T44" t="n">
+        <v>2</v>
+      </c>
+      <c r="U44" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="45">
@@ -2985,22 +3524,22 @@
         <v>9.390000000000001</v>
       </c>
       <c r="G45" s="1" t="n">
-        <v>45762.38541666666</v>
+        <v>45762.55208333334</v>
       </c>
       <c r="H45" t="n">
-        <v>354.85</v>
+        <v>361.75</v>
       </c>
       <c r="I45" t="n">
         <v>358.04189816361</v>
       </c>
       <c r="J45" s="2" t="n">
-        <v>8</v>
+        <v>8.166666666666666</v>
       </c>
       <c r="K45" t="n">
-        <v>-8.42</v>
+        <v>-10.53</v>
       </c>
       <c r="L45" t="n">
-        <v>9.210000000000001</v>
+        <v>10.6</v>
       </c>
       <c r="M45" t="n">
         <v>2.73</v>
@@ -3015,7 +3554,19 @@
         <v>0</v>
       </c>
       <c r="Q45" t="n">
-        <v>9</v>
+        <v>10</v>
+      </c>
+      <c r="R45" s="3" t="n">
+        <v>45771</v>
+      </c>
+      <c r="S45" t="b">
+        <v>0</v>
+      </c>
+      <c r="T45" t="n">
+        <v>1</v>
+      </c>
+      <c r="U45" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="46">
@@ -3042,22 +3593,22 @@
         <v>9.460000000000001</v>
       </c>
       <c r="G46" s="1" t="n">
-        <v>45777.38541666666</v>
+        <v>45777.55208333334</v>
       </c>
       <c r="H46" t="n">
-        <v>353.3</v>
+        <v>347.6</v>
       </c>
       <c r="I46" t="n">
         <v>352.1139490032976</v>
       </c>
       <c r="J46" s="2" t="n">
-        <v>14.83333333333333</v>
+        <v>15</v>
       </c>
       <c r="K46" t="n">
-        <v>-2.34</v>
+        <v>-3.91</v>
       </c>
       <c r="L46" t="n">
-        <v>2.5</v>
+        <v>4.6</v>
       </c>
       <c r="M46" t="n">
         <v>0.83</v>
@@ -3072,7 +3623,19 @@
         <v>1</v>
       </c>
       <c r="Q46" t="n">
-        <v>20</v>
+        <v>21</v>
+      </c>
+      <c r="R46" s="3" t="n">
+        <v>45771</v>
+      </c>
+      <c r="S46" t="b">
+        <v>1</v>
+      </c>
+      <c r="T46" t="n">
+        <v>2</v>
+      </c>
+      <c r="U46" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="47">
@@ -3099,28 +3662,28 @@
         <v>7.52</v>
       </c>
       <c r="G47" s="1" t="n">
-        <v>45786.55208333334</v>
+        <v>45789.38541666666</v>
       </c>
       <c r="H47" t="n">
-        <v>324.95</v>
+        <v>351.95</v>
       </c>
       <c r="I47" t="n">
         <v>347.4623789683118</v>
       </c>
       <c r="J47" s="2" t="n">
-        <v>9</v>
+        <v>11.83333333333333</v>
       </c>
       <c r="K47" t="n">
-        <v>6.52</v>
+        <v>-1.25</v>
       </c>
       <c r="L47" t="n">
         <v>5.19</v>
       </c>
       <c r="M47" t="n">
-        <v>1.01</v>
+        <v>4.02</v>
       </c>
       <c r="N47" t="n">
-        <v>1.14</v>
+        <v>10.97</v>
       </c>
       <c r="O47" t="n">
         <v>-3.55</v>
@@ -3129,7 +3692,19 @@
         <v>0</v>
       </c>
       <c r="Q47" t="n">
-        <v>13</v>
+        <v>14</v>
+      </c>
+      <c r="R47" s="3" t="n">
+        <v>45806</v>
+      </c>
+      <c r="S47" t="b">
+        <v>0</v>
+      </c>
+      <c r="T47" t="n">
+        <v>1</v>
+      </c>
+      <c r="U47" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="48">
@@ -3156,19 +3731,19 @@
         <v>10.76</v>
       </c>
       <c r="G48" s="1" t="n">
-        <v>45825.38541666666</v>
+        <v>45825.55208333334</v>
       </c>
       <c r="H48" t="n">
-        <v>403.65</v>
+        <v>399.9</v>
       </c>
       <c r="I48" t="n">
         <v>403.3983883840945</v>
       </c>
       <c r="J48" s="2" t="n">
-        <v>36</v>
+        <v>36.16666666666666</v>
       </c>
       <c r="K48" t="n">
-        <v>14.69</v>
+        <v>13.62</v>
       </c>
       <c r="L48" t="n">
         <v>4.25</v>
@@ -3186,7 +3761,19 @@
         <v>1</v>
       </c>
       <c r="Q48" t="n">
-        <v>53</v>
+        <v>54</v>
+      </c>
+      <c r="R48" s="3" t="n">
+        <v>45806</v>
+      </c>
+      <c r="S48" t="b">
+        <v>1</v>
+      </c>
+      <c r="T48" t="n">
+        <v>2</v>
+      </c>
+      <c r="U48" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="49">
@@ -3213,19 +3800,19 @@
         <v>7.59</v>
       </c>
       <c r="G49" s="1" t="n">
-        <v>45901.55208333334</v>
+        <v>45902.38541666666</v>
       </c>
       <c r="H49" t="n">
-        <v>316.3</v>
+        <v>338.35</v>
       </c>
       <c r="I49" t="n">
         <v>320.1702243736874</v>
       </c>
       <c r="J49" s="2" t="n">
-        <v>76</v>
+        <v>76.83333333333333</v>
       </c>
       <c r="K49" t="n">
-        <v>20.91</v>
+        <v>15.39</v>
       </c>
       <c r="L49" t="n">
         <v>1.4</v>
@@ -3234,7 +3821,7 @@
         <v>1.62</v>
       </c>
       <c r="N49" t="n">
-        <v>4.41</v>
+        <v>4.69</v>
       </c>
       <c r="O49" t="n">
         <v>-2.48</v>
@@ -3243,7 +3830,19 @@
         <v>0</v>
       </c>
       <c r="Q49" t="n">
-        <v>105</v>
+        <v>106</v>
+      </c>
+      <c r="R49" s="3" t="n">
+        <v>45834</v>
+      </c>
+      <c r="S49" t="b">
+        <v>1</v>
+      </c>
+      <c r="T49" t="n">
+        <v>4</v>
+      </c>
+      <c r="U49" t="n">
+        <v>3</v>
       </c>
     </row>
     <row r="50">
@@ -3270,19 +3869,19 @@
         <v>9.99</v>
       </c>
       <c r="G50" s="1" t="n">
-        <v>45925.55208333334</v>
+        <v>45926.38541666666</v>
       </c>
       <c r="H50" t="n">
-        <v>346.25</v>
+        <v>340.75</v>
       </c>
       <c r="I50" t="n">
         <v>344.0954764798467</v>
       </c>
       <c r="J50" s="2" t="n">
-        <v>23.16666666666667</v>
+        <v>24</v>
       </c>
       <c r="K50" t="n">
-        <v>2.33</v>
+        <v>0.71</v>
       </c>
       <c r="L50" t="n">
         <v>6.61</v>
@@ -3300,7 +3899,19 @@
         <v>1</v>
       </c>
       <c r="Q50" t="n">
-        <v>36</v>
+        <v>37</v>
+      </c>
+      <c r="R50" s="3" t="n">
+        <v>45930</v>
+      </c>
+      <c r="S50" t="b">
+        <v>0</v>
+      </c>
+      <c r="T50" t="n">
+        <v>1</v>
+      </c>
+      <c r="U50" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="51">
@@ -3327,19 +3938,19 @@
         <v>7</v>
       </c>
       <c r="G51" s="1" t="n">
-        <v>45985.38541666666</v>
+        <v>45985.55208333334</v>
       </c>
       <c r="H51" t="n">
-        <v>314.65</v>
+        <v>328.6</v>
       </c>
       <c r="I51" t="n">
         <v>328.4438843703128</v>
       </c>
       <c r="J51" s="2" t="n">
-        <v>59</v>
+        <v>59.16666666666666</v>
       </c>
       <c r="K51" t="n">
-        <v>7.66</v>
+        <v>3.57</v>
       </c>
       <c r="L51" t="n">
         <v>4.89</v>
@@ -3357,7 +3968,19 @@
         <v>0</v>
       </c>
       <c r="Q51" t="n">
-        <v>76</v>
+        <v>77</v>
+      </c>
+      <c r="R51" s="3" t="n">
+        <v>45930</v>
+      </c>
+      <c r="S51" t="b">
+        <v>1</v>
+      </c>
+      <c r="T51" t="n">
+        <v>3</v>
+      </c>
+      <c r="U51" t="n">
+        <v>3</v>
       </c>
     </row>
     <row r="52">
@@ -3384,22 +4007,22 @@
         <v>7.62</v>
       </c>
       <c r="G52" s="1" t="n">
-        <v>45996.55208333334</v>
+        <v>45999.38541666666</v>
       </c>
       <c r="H52" t="n">
-        <v>311.6</v>
+        <v>303.45</v>
       </c>
       <c r="I52" t="n">
         <v>307.8716925558419</v>
       </c>
       <c r="J52" s="2" t="n">
-        <v>11</v>
+        <v>13.83333333333333</v>
       </c>
       <c r="K52" t="n">
-        <v>-5.17</v>
+        <v>-7.65</v>
       </c>
       <c r="L52" t="n">
-        <v>6.31</v>
+        <v>7.71</v>
       </c>
       <c r="M52" t="n">
         <v>1.54</v>
@@ -3414,7 +4037,19 @@
         <v>1</v>
       </c>
       <c r="Q52" t="n">
-        <v>19</v>
+        <v>20</v>
+      </c>
+      <c r="R52" s="3" t="n">
+        <v>45986</v>
+      </c>
+      <c r="S52" t="b">
+        <v>1</v>
+      </c>
+      <c r="T52" t="n">
+        <v>2</v>
+      </c>
+      <c r="U52" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="53">
@@ -3441,22 +4076,22 @@
         <v>6.04</v>
       </c>
       <c r="G53" s="1" t="n">
-        <v>46010.38541666666</v>
+        <v>46010.55208333334</v>
       </c>
       <c r="H53" t="n">
-        <v>310.55</v>
+        <v>319.15</v>
       </c>
       <c r="I53" t="n">
         <v>316.5908682790993</v>
       </c>
       <c r="J53" s="2" t="n">
-        <v>11</v>
+        <v>11.16666666666667</v>
       </c>
       <c r="K53" t="n">
-        <v>-2.34</v>
+        <v>-5.17</v>
       </c>
       <c r="L53" t="n">
-        <v>4.14</v>
+        <v>5.68</v>
       </c>
       <c r="M53" t="n">
         <v>1.21</v>
@@ -3471,7 +4106,19 @@
         <v>0</v>
       </c>
       <c r="Q53" t="n">
-        <v>19</v>
+        <v>20</v>
+      </c>
+      <c r="R53" s="3" t="n">
+        <v>46021</v>
+      </c>
+      <c r="S53" t="b">
+        <v>0</v>
+      </c>
+      <c r="T53" t="n">
+        <v>1</v>
+      </c>
+      <c r="U53" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="54">
@@ -3498,19 +4145,19 @@
         <v>5.52</v>
       </c>
       <c r="G54" s="1" t="n">
-        <v>46029.55208333334</v>
+        <v>46030.38541666666</v>
       </c>
       <c r="H54" t="n">
-        <v>357.3</v>
+        <v>346.55</v>
       </c>
       <c r="I54" t="n">
         <v>354.3882279643841</v>
       </c>
       <c r="J54" s="2" t="n">
-        <v>19</v>
+        <v>19.83333333333333</v>
       </c>
       <c r="K54" t="n">
-        <v>11.95</v>
+        <v>8.59</v>
       </c>
       <c r="L54" t="n">
         <v>2.69</v>
@@ -3528,7 +4175,19 @@
         <v>1</v>
       </c>
       <c r="Q54" t="n">
-        <v>25</v>
+        <v>26</v>
+      </c>
+      <c r="R54" s="3" t="n">
+        <v>46021</v>
+      </c>
+      <c r="S54" t="b">
+        <v>1</v>
+      </c>
+      <c r="T54" t="n">
+        <v>2</v>
+      </c>
+      <c r="U54" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="55">
@@ -3555,19 +4214,19 @@
         <v>9.65</v>
       </c>
       <c r="G55" s="1" t="n">
-        <v>46050.38541666666</v>
+        <v>46050.55208333334</v>
       </c>
       <c r="H55" t="n">
-        <v>338.45</v>
+        <v>344.15</v>
       </c>
       <c r="I55" t="n">
         <v>340.1803740104679</v>
       </c>
       <c r="J55" s="2" t="n">
-        <v>20</v>
+        <v>20.16666666666667</v>
       </c>
       <c r="K55" t="n">
-        <v>2.34</v>
+        <v>0.6899999999999999</v>
       </c>
       <c r="L55" t="n">
         <v>4.1</v>
@@ -3585,7 +4244,19 @@
         <v>1</v>
       </c>
       <c r="Q55" t="n">
-        <v>25</v>
+        <v>26</v>
+      </c>
+      <c r="R55" s="3" t="n">
+        <v>46049</v>
+      </c>
+      <c r="S55" t="b">
+        <v>1</v>
+      </c>
+      <c r="T55" t="n">
+        <v>2</v>
+      </c>
+      <c r="U55" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="56">
@@ -3612,25 +4283,25 @@
         <v>8.199999999999999</v>
       </c>
       <c r="G56" s="1" t="n">
-        <v>46054.55208333334</v>
+        <v>46055.38541666666</v>
       </c>
       <c r="H56" t="n">
-        <v>326.95</v>
+        <v>314.75</v>
       </c>
       <c r="I56" t="n">
         <v>315.9212199279574</v>
       </c>
       <c r="J56" s="2" t="n">
-        <v>4</v>
+        <v>4.833333333333333</v>
       </c>
       <c r="K56" t="n">
-        <v>-5</v>
+        <v>-8.539999999999999</v>
       </c>
       <c r="L56" t="n">
         <v>10.18</v>
       </c>
       <c r="M56" t="n">
-        <v>0.62</v>
+        <v>2.13</v>
       </c>
       <c r="N56" t="n">
         <v>4.96</v>
@@ -3642,7 +4313,19 @@
         <v>1</v>
       </c>
       <c r="Q56" t="n">
-        <v>7</v>
+        <v>8</v>
+      </c>
+      <c r="R56" s="3" t="n">
+        <v>46077</v>
+      </c>
+      <c r="S56" t="b">
+        <v>0</v>
+      </c>
+      <c r="T56" t="n">
+        <v>1</v>
+      </c>
+      <c r="U56" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="57">
@@ -3669,19 +4352,19 @@
         <v>13.04</v>
       </c>
       <c r="G57" s="1" t="n">
-        <v>46105.55208333334</v>
+        <v>46106.38541666666</v>
       </c>
       <c r="H57" t="n">
-        <v>258.55</v>
+        <v>272</v>
       </c>
       <c r="I57" t="n">
         <v>271.9450296946861</v>
       </c>
       <c r="J57" s="2" t="n">
-        <v>50.16666666666666</v>
+        <v>51</v>
       </c>
       <c r="K57" t="n">
-        <v>17.86</v>
+        <v>13.58</v>
       </c>
       <c r="L57" t="n">
         <v>7.7</v>
@@ -3690,7 +4373,7 @@
         <v>3.66</v>
       </c>
       <c r="N57" t="n">
-        <v>3.48</v>
+        <v>4.18</v>
       </c>
       <c r="O57" t="n">
         <v>-0.6899999999999999</v>
@@ -3699,7 +4382,19 @@
         <v>0</v>
       </c>
       <c r="Q57" t="n">
-        <v>72</v>
+        <v>73</v>
+      </c>
+      <c r="R57" s="3" t="n">
+        <v>46077</v>
+      </c>
+      <c r="S57" t="b">
+        <v>1</v>
+      </c>
+      <c r="T57" t="n">
+        <v>2</v>
+      </c>
+      <c r="U57" t="n">
+        <v>2</v>
       </c>
     </row>
     <row r="58">
@@ -3726,19 +4421,19 @@
         <v>10.38</v>
       </c>
       <c r="G58" s="1" t="n">
-        <v>46153.55208333334</v>
+        <v>46154.38541666666</v>
       </c>
       <c r="H58" t="n">
-        <v>295.85</v>
+        <v>287.8</v>
       </c>
       <c r="I58" t="n">
         <v>291.0406969216702</v>
       </c>
       <c r="J58" s="2" t="n">
-        <v>47.16666666666666</v>
+        <v>48</v>
       </c>
       <c r="K58" t="n">
-        <v>8.77</v>
+        <v>5.81</v>
       </c>
       <c r="L58" t="n">
         <v>8.82</v>
@@ -3756,7 +4451,19 @@
         <v>1</v>
       </c>
       <c r="Q58" t="n">
-        <v>58</v>
+        <v>59</v>
+      </c>
+      <c r="R58" s="3" t="n">
+        <v>46111</v>
+      </c>
+      <c r="S58" t="b">
+        <v>1</v>
+      </c>
+      <c r="T58" t="n">
+        <v>3</v>
+      </c>
+      <c r="U58" t="n">
+        <v>2</v>
       </c>
     </row>
     <row r="59">
@@ -3783,25 +4490,25 @@
         <v>7.74</v>
       </c>
       <c r="G59" s="1" t="n">
-        <v>46185.55208333334</v>
+        <v>46188.38541666666</v>
       </c>
       <c r="H59" t="n">
-        <v>233.9</v>
+        <v>242.6</v>
       </c>
       <c r="I59" t="n">
         <v>236.9951819681957</v>
       </c>
       <c r="J59" s="2" t="n">
-        <v>31.16666666666667</v>
+        <v>34</v>
       </c>
       <c r="K59" t="n">
-        <v>18.73</v>
+        <v>15.71</v>
       </c>
       <c r="L59" t="n">
         <v>3.04</v>
       </c>
       <c r="M59" t="n">
-        <v>2.56</v>
+        <v>3.46</v>
       </c>
       <c r="N59" t="n">
         <v>4.98</v>
@@ -3813,7 +4520,19 @@
         <v>0</v>
       </c>
       <c r="Q59" t="n">
-        <v>46</v>
+        <v>47</v>
+      </c>
+      <c r="R59" s="3" t="n">
+        <v>46168</v>
+      </c>
+      <c r="S59" t="b">
+        <v>1</v>
+      </c>
+      <c r="T59" t="n">
+        <v>2</v>
+      </c>
+      <c r="U59" t="n">
+        <v>2</v>
       </c>
     </row>
     <row r="60">
@@ -3840,22 +4559,22 @@
         <v>7.59</v>
       </c>
       <c r="G60" s="1" t="n">
-        <v>46206.55208333334</v>
+        <v>46209.38541666666</v>
       </c>
       <c r="H60" t="n">
-        <v>235.53</v>
+        <v>234.28</v>
       </c>
       <c r="I60" t="n">
         <v>234.7750831848856</v>
       </c>
       <c r="J60" s="2" t="n">
-        <v>18.16666666666667</v>
+        <v>21</v>
       </c>
       <c r="K60" t="n">
-        <v>-2.91</v>
+        <v>-3.43</v>
       </c>
       <c r="L60" t="n">
-        <v>3.09</v>
+        <v>3.99</v>
       </c>
       <c r="M60" t="n">
         <v>0.24</v>
@@ -3870,7 +4589,19 @@
         <v>0</v>
       </c>
       <c r="Q60" t="n">
-        <v>28</v>
+        <v>29</v>
+      </c>
+      <c r="R60" s="3" t="n">
+        <v>46203</v>
+      </c>
+      <c r="S60" t="b">
+        <v>1</v>
+      </c>
+      <c r="T60" t="n">
+        <v>2</v>
+      </c>
+      <c r="U60" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="61">
@@ -3897,19 +4628,19 @@
         <v>3.91</v>
       </c>
       <c r="G61" s="1" t="n">
-        <v>46234.55208333334</v>
+        <v>46237.38541666666</v>
       </c>
       <c r="H61" t="n">
-        <v>225.1</v>
+        <v>229.73</v>
       </c>
       <c r="I61" t="n">
         <v>229.6812863171178</v>
       </c>
       <c r="J61" s="2" t="n">
-        <v>25.16666666666667</v>
+        <v>28</v>
       </c>
       <c r="K61" t="n">
-        <v>3.92</v>
+        <v>1.94</v>
       </c>
       <c r="L61" t="n">
         <v>1.11</v>
@@ -3918,7 +4649,7 @@
         <v>1.26</v>
       </c>
       <c r="N61" t="n">
-        <v>2.64</v>
+        <v>3.47</v>
       </c>
       <c r="O61" t="n">
         <v>-0.5600000000000001</v>
@@ -3927,7 +4658,19 @@
         <v>0</v>
       </c>
       <c r="Q61" t="n">
-        <v>40</v>
+        <v>41</v>
+      </c>
+      <c r="R61" s="3" t="n">
+        <v>46231</v>
+      </c>
+      <c r="S61" t="b">
+        <v>1</v>
+      </c>
+      <c r="T61" t="n">
+        <v>2</v>
+      </c>
+      <c r="U61" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="62">
@@ -3954,19 +4697,19 @@
         <v>4.85</v>
       </c>
       <c r="G62" s="1" t="n">
-        <v>46253.38541666666</v>
+        <v>46253.55208333334</v>
       </c>
       <c r="H62" t="n">
-        <v>223.69</v>
+        <v>223.5</v>
       </c>
       <c r="I62" t="n">
         <v>223.6160051931382</v>
       </c>
       <c r="J62" s="2" t="n">
-        <v>16</v>
+        <v>16.16666666666667</v>
       </c>
       <c r="K62" t="n">
-        <v>-2.63</v>
+        <v>-2.71</v>
       </c>
       <c r="L62" t="n">
         <v>3.69</v>
@@ -3984,7 +4727,19 @@
         <v>0</v>
       </c>
       <c r="Q62" t="n">
-        <v>25</v>
+        <v>26</v>
+      </c>
+      <c r="R62" s="3" t="n">
+        <v>46259</v>
+      </c>
+      <c r="S62" t="b">
+        <v>0</v>
+      </c>
+      <c r="T62" t="n">
+        <v>1</v>
+      </c>
+      <c r="U62" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="63">
@@ -4011,19 +4766,19 @@
         <v>4.16</v>
       </c>
       <c r="G63" s="1" t="n">
-        <v>46282.55208333334</v>
+        <v>46283.38541666666</v>
       </c>
       <c r="H63" t="n">
-        <v>201.75</v>
+        <v>207.42</v>
       </c>
       <c r="I63" t="n">
         <v>207.0926383736293</v>
       </c>
       <c r="J63" s="2" t="n">
-        <v>29</v>
+        <v>29.83333333333333</v>
       </c>
       <c r="K63" t="n">
-        <v>9.73</v>
+        <v>7.19</v>
       </c>
       <c r="L63" t="n">
         <v>3.53</v>
@@ -4032,7 +4787,7 @@
         <v>1.23</v>
       </c>
       <c r="N63" t="n">
-        <v>2.15</v>
+        <v>4.24</v>
       </c>
       <c r="O63" t="n">
         <v>-0.84</v>
@@ -4041,7 +4796,19 @@
         <v>0</v>
       </c>
       <c r="Q63" t="n">
-        <v>41</v>
+        <v>42</v>
+      </c>
+      <c r="R63" s="3" t="n">
+        <v>46259</v>
+      </c>
+      <c r="S63" t="b">
+        <v>1</v>
+      </c>
+      <c r="T63" t="n">
+        <v>2</v>
+      </c>
+      <c r="U63" t="n">
+        <v>2</v>
       </c>
     </row>
     <row r="64">
@@ -4068,22 +4835,22 @@
         <v>6.78</v>
       </c>
       <c r="G64" s="1" t="n">
-        <v>46293.55208333334</v>
+        <v>46294.38541666666</v>
       </c>
       <c r="H64" t="n">
-        <v>202.39</v>
+        <v>199.68</v>
       </c>
       <c r="I64" t="n">
         <v>202.2063680563836</v>
       </c>
       <c r="J64" s="2" t="n">
-        <v>10.16666666666667</v>
+        <v>11</v>
       </c>
       <c r="K64" t="n">
-        <v>-2.43</v>
+        <v>-3.73</v>
       </c>
       <c r="L64" t="n">
-        <v>3.2</v>
+        <v>5.83</v>
       </c>
       <c r="M64" t="n">
         <v>0.87</v>
@@ -4098,7 +4865,19 @@
         <v>1</v>
       </c>
       <c r="Q64" t="n">
-        <v>14</v>
+        <v>15</v>
+      </c>
+      <c r="R64" s="3" t="n">
+        <v>46294</v>
+      </c>
+      <c r="S64" t="b">
+        <v>0</v>
+      </c>
+      <c r="T64" t="n">
+        <v>1</v>
+      </c>
+      <c r="U64" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="65">
@@ -4125,19 +4904,19 @@
         <v>4.83</v>
       </c>
       <c r="G65" s="1" t="n">
-        <v>46310.55208333334</v>
+        <v>46311.38541666666</v>
       </c>
       <c r="H65" t="n">
-        <v>196.2</v>
+        <v>201.32</v>
       </c>
       <c r="I65" t="n">
         <v>200.3628882538897</v>
       </c>
       <c r="J65" s="2" t="n">
-        <v>16.16666666666667</v>
+        <v>17</v>
       </c>
       <c r="K65" t="n">
-        <v>1.74</v>
+        <v>-0.82</v>
       </c>
       <c r="L65" t="n">
         <v>4.99</v>
@@ -4155,7 +4934,19 @@
         <v>0</v>
       </c>
       <c r="Q65" t="n">
-        <v>24</v>
+        <v>25</v>
+      </c>
+      <c r="R65" s="3" t="n">
+        <v>46322</v>
+      </c>
+      <c r="S65" t="b">
+        <v>0</v>
+      </c>
+      <c r="T65" t="n">
+        <v>1</v>
+      </c>
+      <c r="U65" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="66">
@@ -4182,28 +4973,28 @@
         <v>6.96</v>
       </c>
       <c r="G66" s="1" t="n">
-        <v>46314.55208333334</v>
+        <v>46316.38541666666</v>
       </c>
       <c r="H66" t="n">
-        <v>194.25</v>
+        <v>187.87</v>
       </c>
       <c r="I66" t="n">
         <v>189.2315704819388</v>
       </c>
       <c r="J66" s="2" t="n">
-        <v>3.166666666666667</v>
+        <v>5</v>
       </c>
       <c r="K66" t="n">
-        <v>-3.51</v>
+        <v>-6.68</v>
       </c>
       <c r="L66" t="n">
-        <v>3.63</v>
+        <v>6.86</v>
       </c>
       <c r="M66" t="n">
         <v>-0</v>
       </c>
       <c r="N66" t="n">
-        <v>2.46</v>
+        <v>3.05</v>
       </c>
       <c r="O66" t="n">
         <v>1.5</v>
@@ -4212,7 +5003,19 @@
         <v>0</v>
       </c>
       <c r="Q66" t="n">
-        <v>4</v>
+        <v>5</v>
+      </c>
+      <c r="R66" s="3" t="n">
+        <v>46322</v>
+      </c>
+      <c r="S66" t="b">
+        <v>0</v>
+      </c>
+      <c r="T66" t="n">
+        <v>1</v>
+      </c>
+      <c r="U66" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="67">
@@ -4263,6 +5066,12 @@
       <c r="Q67" t="n">
         <v>10</v>
       </c>
+      <c r="R67" s="3" t="n">
+        <v>46322</v>
+      </c>
+      <c r="S67" t="inlineStr"/>
+      <c r="T67" t="inlineStr"/>
+      <c r="U67" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
@@ -6365,7 +7174,7 @@
         </is>
       </c>
       <c r="B5" t="n">
-        <v>25.6</v>
+        <v>26.8</v>
       </c>
     </row>
     <row r="6">
@@ -6375,7 +7184,7 @@
         </is>
       </c>
       <c r="B6" t="n">
-        <v>20</v>
+        <v>21</v>
       </c>
     </row>
     <row r="7">
@@ -6385,7 +7194,7 @@
         </is>
       </c>
       <c r="B7" t="n">
-        <v>79.8</v>
+        <v>80</v>
       </c>
     </row>
     <row r="8">
@@ -6395,7 +7204,7 @@
         </is>
       </c>
       <c r="B8" t="n">
-        <v>3.2</v>
+        <v>4.8</v>
       </c>
     </row>
     <row r="9">
@@ -6405,7 +7214,7 @@
         </is>
       </c>
       <c r="B9" t="n">
-        <v>33.2</v>
+        <v>34</v>
       </c>
     </row>
     <row r="10">
@@ -6415,7 +7224,7 @@
         </is>
       </c>
       <c r="B10" t="n">
-        <v>49</v>
+        <v>49.8</v>
       </c>
     </row>
     <row r="11">
@@ -6455,7 +7264,7 @@
         </is>
       </c>
       <c r="B14" t="n">
-        <v>7.37</v>
+        <v>3.52</v>
       </c>
     </row>
     <row r="15">
@@ -6465,7 +7274,7 @@
         </is>
       </c>
       <c r="B15" t="n">
-        <v>10.94</v>
+        <v>7.13</v>
       </c>
     </row>
     <row r="16">
@@ -6475,7 +7284,7 @@
         </is>
       </c>
       <c r="B16" t="n">
-        <v>3.69</v>
+        <v>-0.21</v>
       </c>
     </row>
     <row r="17">
@@ -6485,7 +7294,7 @@
         </is>
       </c>
       <c r="B17" t="n">
-        <v>94.22</v>
+        <v>86.8</v>
       </c>
     </row>
     <row r="18">
@@ -6495,7 +7304,7 @@
         </is>
       </c>
       <c r="B18" t="n">
-        <v>56.9</v>
+        <v>47.7</v>
       </c>
     </row>
     <row r="19">
@@ -6505,7 +7314,7 @@
         </is>
       </c>
       <c r="B19" t="n">
-        <v>5.44</v>
+        <v>6.4</v>
       </c>
     </row>
     <row r="20">
@@ -6515,7 +7324,7 @@
         </is>
       </c>
       <c r="B20" t="n">
-        <v>4.54</v>
+        <v>5.19</v>
       </c>
     </row>
     <row r="21">
@@ -6525,7 +7334,7 @@
         </is>
       </c>
       <c r="B21" t="n">
-        <v>16.67</v>
+        <v>20.7</v>
       </c>
     </row>
     <row r="22">
@@ -6535,7 +7344,7 @@
         </is>
       </c>
       <c r="B22" t="n">
-        <v>27</v>
+        <v>35</v>
       </c>
     </row>
     <row r="23">
@@ -6545,7 +7354,7 @@
         </is>
       </c>
       <c r="B23" t="n">
-        <v>5</v>
+        <v>10</v>
       </c>
     </row>
     <row r="24">
@@ -6555,7 +7364,7 @@
         </is>
       </c>
       <c r="B24" t="n">
-        <v>2.13</v>
+        <v>2.67</v>
       </c>
     </row>
     <row r="25">
@@ -6565,7 +7374,7 @@
         </is>
       </c>
       <c r="B25" t="n">
-        <v>7.37</v>
+        <v>13.2</v>
       </c>
     </row>
     <row r="26">
@@ -6575,7 +7384,7 @@
         </is>
       </c>
       <c r="B26" t="n">
-        <v>4.46</v>
+        <v>5.31</v>
       </c>
     </row>
     <row r="27">
@@ -6585,7 +7394,7 @@
         </is>
       </c>
       <c r="B27" t="n">
-        <v>12.47</v>
+        <v>13.22</v>
       </c>
     </row>
     <row r="28">
@@ -6595,7 +7404,7 @@
         </is>
       </c>
       <c r="B28" t="n">
-        <v>32</v>
+        <v>41</v>
       </c>
     </row>
     <row r="29">
